--- a/nriss-patch-1/ig/StructureDefinition-fr-core-appointment.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-core-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:55:04+00:00</t>
+    <t>2026-02-24T08:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/StructureDefinition-fr-core-appointment.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-core-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T10:29:07+00:00</t>
+    <t>2026-06-05T13:13:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
